--- a/04_DESIGN_TABLES/DesignTable_2406.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2406.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3614,12 +3619,17 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p007-t03: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.02 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2406-20-12</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3702,17 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p008-t01: agrees on HEXB@HEX, D3@BORE; DIFFERS on L23@DRIVE 2.01 vs Brennan L0 LGTH 2.000 (built to the dimension source, s6)</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2406-20-16</t>
         </is>
       </c>
     </row>
@@ -4610,24 +4625,70 @@
           <t>2406-03-04</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="K52" t="n">
+        <v>60</v>
+      </c>
+      <c r="L52" t="n">
+        <v>37</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.125</v>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>2406-03-04</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>3/8-24 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>7/16-20</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "L0 LGTH" = "0.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 16/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (31 differ, e.g. 2406-04-05 1.0 vs 1.15); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "C HEX" = "0.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 46/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2406-04-05 0.56 vs 0.625); D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 "2406 FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-03-04 col "B2 DRILL" = "0.125" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 183.5, page verified) [Brennan = yes 2026-10-18] - male-end bore; mapping: TFA p7 2406 drawing: L0 spans the whole part (female face to male JIC tip), C HEX = body hex, B2 DRILL = male-end bore (impact/F2a.json certain; drawing re-read 2026-10-18, verify/png/TFA_p07_RT.png); same-table check on today's base: 45/47 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 2406-05-06 0.3 vs 0.234); THDMAJ_A@DRIVE: end library gen_straight2 JIC[3] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major of the female end (first dash); THDMAJ_B@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major of the male end (second dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[3] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2406 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L23 / hex / D3 from the Brennan TFA catalog p7 alone (built 2406 rows are Air-Way; Brennan L0 equals their L23 on 16/47 only - different bodies, see wave2 REPORT); female -03 port = JICF_MEAS[3] (Brennan 2406-03-04 STEP, already in the end library)</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -4638,6 +4699,11 @@
       <c r="U52" t="inlineStr">
         <is>
           <t>2406-03-04</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4647,24 +4713,70 @@
           <t>2406-04-02</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="K53" t="n">
+        <v>60</v>
+      </c>
+      <c r="L53" t="n">
+        <v>37</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.062</v>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>2406-04-02</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>7/16-20 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5/16-24</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'L0 LGTH' = 1.04 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'C HEX' = 0.563 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-02 column 'B2 DRILL' = 0.062 (catalog_verified.json); OMi Items row 571: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 5/16-24; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[2] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -4675,6 +4787,11 @@
       <c r="U53" t="inlineStr">
         <is>
           <t>2406-04-02</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4684,24 +4801,70 @@
           <t>2406-04-04</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="K54" t="n">
+        <v>60</v>
+      </c>
+      <c r="L54" t="n">
+        <v>37</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.172</v>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>2406-04-04</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>7/16-20 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7/16-20</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'L0 LGTH' = 1.15 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'C HEX' = 0.562 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-04 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 572: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/16-20; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -4712,6 +4875,11 @@
       <c r="U54" t="inlineStr">
         <is>
           <t>2406-04-04</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4721,24 +4889,70 @@
           <t>2406-04-08</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K55" t="n">
+        <v>60</v>
+      </c>
+      <c r="L55" t="n">
+        <v>37</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.172</v>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>2406-04-08</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>7/16-20 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'L0 LGTH' = 1.25 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'C HEX' = 0.812 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-04-08 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 574: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/16-20; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 3/4-16; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -4749,6 +4963,11 @@
       <c r="U55" t="inlineStr">
         <is>
           <t>2406-04-08</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4758,24 +4977,70 @@
           <t>2406-06-10</t>
         </is>
       </c>
+      <c r="B56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K56" t="n">
+        <v>60</v>
+      </c>
+      <c r="L56" t="n">
+        <v>37</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.297</v>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t>2406-06-10</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>9/16-18 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'L0 LGTH' = 1.38 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'C HEX' = 0.937 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-06-10 column 'B2 DRILL' = 0.297 (catalog_verified.json); OMi Items row 581: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 9/16-18; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/8-14; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -4786,6 +5051,11 @@
       <c r="U56" t="inlineStr">
         <is>
           <t>2406-06-10</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4832,24 +5102,70 @@
           <t>2406-08-08</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K58" t="n">
+        <v>60</v>
+      </c>
+      <c r="L58" t="n">
+        <v>37</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.391</v>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>2406-08-08</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>3/4-16 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'L0 LGTH' = 1.41 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'C HEX' = 0.875 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-08-08 column 'B2 DRILL' = 0.391 (catalog_verified.json); OMi Items row 585: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 3/4-16; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 3/4-16; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -4860,6 +5176,11 @@
       <c r="U58" t="inlineStr">
         <is>
           <t>2406-08-08</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4869,24 +5190,70 @@
           <t>2406-10-16</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K59" t="n">
+        <v>60</v>
+      </c>
+      <c r="L59" t="n">
+        <v>37</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.484</v>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
           <t>2406-10-16</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>7/8-14 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'L0 LGTH' = 1.76 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'C HEX' = 1.375 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-10-16 column 'B2 DRILL' = 0.484 (catalog_verified.json); OMi Items row 594: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 7/8-14; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 1-5/16-12; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -4897,6 +5264,11 @@
       <c r="U59" t="inlineStr">
         <is>
           <t>2406-10-16</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4906,24 +5278,70 @@
           <t>2406-12-04</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="K60" t="n">
+        <v>60</v>
+      </c>
+      <c r="L60" t="n">
+        <v>37</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.172</v>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>2406-12-04</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>7/16-20</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'L0 LGTH' = 1.50 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'C HEX' = 1.250 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-04 column 'B2 DRILL' = 0.172 (catalog_verified.json); OMi Items row 595: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 1-1/16-12; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 7/16-20; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4934,6 +5352,11 @@
       <c r="U60" t="inlineStr">
         <is>
           <t>2406-12-04</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -4943,24 +5366,70 @@
           <t>2406-12-12</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K61" t="n">
+        <v>60</v>
+      </c>
+      <c r="L61" t="n">
+        <v>37</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.609</v>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>2406-12-12</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female JIC)</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L23@DRIVE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'L0 LGTH' = 1.77 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'C HEX' = 1.250 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p7 table TFA-p007-t03 (FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)) row 2406-12-12 column 'B2 DRILL' = 0.609 (catalog_verified.json); OMi Items row 599: no dimension; no Air-Way row; equals the 2026-10-02 proposal; THDMAJ_A@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, female end (first dash); catalog B1 1-1/16-12; equals the 2026-10-02 proposal; THDMAJ_B@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male end (second dash); catalog B2 1-1/16-12; equals the 2026-10-02 proposal; JICB_RELIEFL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) RL; equals the 2026-10-02 proposal; JICB_THDZ@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) TZ; equals the 2026-10-02 proposal; JICB_CONEDIA@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) CD; equals the 2026-10-02 proposal; JICB_LANDL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) LL; equals the 2026-10-02 proposal; JICB_SEATL@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) SL; equals the 2026-10-02 proposal; RELIEFANG@DRIVE: gen_straight2 end_JICM constant (60 deg relief ramp, every 2406 row); equals the 2026-10-02 proposal; SEATB@DRIVE: gen_straight2 end_JICM constant (37 deg flare seat, every 2406 row); equals the 2026-10-02 proposal; $PRP@EndA_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text (format of the built 2406 rows); equals the 2026-10-02 proposal; $PRP@EndB_Thread: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone; built rows of this table are Air-Way</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -4971,6 +5440,11 @@
       <c r="U61" t="inlineStr">
         <is>
           <t>2406-12-12</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2406.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2406.xlsx
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>1.5</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source)</t>
+          <t>[BRENNAN-CELL 2026-10-20: L23@DRIVE] Male JIC end: MS33656J==Brennan (VERIFIED); L23/hex/bore: Air-Way (single source); L23@DRIVE: Brennan TFA catalog p.7 table TFA-p007-t03 "FJ-MJ STRAIGHT REDUCER (NON-SWIVEL)" row 2406-16-04 col "L0 LGTH" = 1.840 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.67: with L23 1.67 the -16 female JIC port (seat measured on the Brennan 2406 STEPs, JICF_MEAS[16]) reaches the -04 male end: radial wall -0.009 at 0.550 from the male tip (generator BLOCKED "wall between the female port and the End A thread root/groove"); same dimension (overall length): L23 = Brennan L0 to rounding on 25 of the 56 2406 rows Brennan prints, Air-Way shorter on most others (2406-16-06 1.65 vs 1.84))</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology.</t>
+          <t>BLOCKED: female-JIC internal end geometry (port depth, internal 37deg seat) UNPUBLISHED - J514/1 paywalled; measure a Brennan 2406 STEP. MS39323 checked: its reducer family does not match this topology. | 2026-10-20 L23@DRIVE = Brennan 1.84 (Air-Way 1.67 cannot be built: with L23 1.67 the -16 female JIC port (seat measured on the Brennan 2406 STEPs, JICF_MEAS[16]) reaches the -04 male end: radial wall -0.009 at 0.550 from the male tip (generator BLOCKED "wall between the female port and the End A thread root/groove"); same dimension (overall length): L23 = Brennan L0 to rounding on 25 of the 56 2406 rows Brennan prints, Air-Way shorter on most others (2406-16-06 1.65 vs 1.84))</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -2800,6 +2800,11 @@
       <c r="U29" t="inlineStr">
         <is>
           <t>2406-16-04</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
